--- a/doc/Consomation Total.xlsx
+++ b/doc/Consomation Total.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{6D37B1DA-F485-43C4-9A4C-41CF1B924667}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{CCE54730-BD2B-40AA-9493-45CA7BCF2E46}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{6D37B1DA-F485-43C4-9A4C-41CF1B924667}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{796C7518-39F7-4B8B-B80A-8032D19E6C2B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2C036080-930E-4B79-8ED5-37F9184B695B}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
   <si>
     <t>Tension[V]</t>
   </si>
@@ -47,15 +47,9 @@
     <t>AC/DC</t>
   </si>
   <si>
-    <t>Bcuk down</t>
-  </si>
-  <si>
     <t>LDO</t>
   </si>
   <si>
-    <t>CM5_3V3</t>
-  </si>
-  <si>
     <t>Consomation 24[V]</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
     <t>24V-I/O</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Front LED</t>
   </si>
   <si>
@@ -101,18 +92,12 @@
     <t>TMUX1204DGSR</t>
   </si>
   <si>
-    <t>Totaux</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>Consomation 3.3[V]</t>
   </si>
   <si>
-    <t>Consomation CM-3.3[V]</t>
-  </si>
-  <si>
     <t>LED activity</t>
   </si>
   <si>
@@ -131,13 +116,19 @@
     <t>Sortie LDO</t>
   </si>
   <si>
-    <t>Alimentations MAX</t>
-  </si>
-  <si>
     <t>Consomation LDO TPS7A2024PDBVR</t>
   </si>
   <si>
-    <t>OK</t>
+    <t>BLOC Alimentations MAX</t>
+  </si>
+  <si>
+    <t>Totaux (&lt;15[W] = OK)</t>
+  </si>
+  <si>
+    <t>Totaux  (&lt;15[W] = OK)</t>
+  </si>
+  <si>
+    <t>Totaux  (&lt;12.5[W] = OK)</t>
   </si>
 </sst>
 </file>
@@ -161,7 +152,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -583,81 +574,21 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
@@ -674,42 +605,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1024,872 +989,760 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4880068-6E37-4936-880D-425D7B9478EC}">
-  <dimension ref="E1:P38"/>
+  <dimension ref="E1:P33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="23.140625" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="26" t="s">
+      <c r="F1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="25" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="14">
         <v>24</v>
       </c>
-      <c r="H2" s="43">
+      <c r="H2" s="25">
         <f>I2/G2</f>
         <v>0.625</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="25">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F3" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="26">
+      <c r="F3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="14">
         <v>5</v>
       </c>
-      <c r="H3" s="43">
+      <c r="H3" s="25">
         <v>2.5</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="25">
         <f>G3*H3</f>
         <v>12.5</v>
       </c>
     </row>
     <row r="4" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F4" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="26">
+      <c r="F4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="14">
         <v>3.3</v>
       </c>
-      <c r="H4" s="43">
+      <c r="H4" s="25">
         <v>0.3</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="25">
         <f>G4*H4</f>
         <v>0.98999999999999988</v>
       </c>
     </row>
-    <row r="5" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F5" s="44" t="s">
+    <row r="5" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F6" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="42">
+        <v>24</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="45"/>
+      <c r="N6" s="46"/>
+    </row>
+    <row r="7" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="41"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="44">
-        <v>3.3</v>
-      </c>
-      <c r="H5" s="45">
-        <v>0.3</v>
-      </c>
-      <c r="I5" s="45">
-        <f>G5*H5</f>
-        <v>0.98999999999999988</v>
-      </c>
-    </row>
-    <row r="6" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F7" s="37" t="s">
+      <c r="K7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="39" t="s">
+      <c r="L7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F8" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8">
+        <f>M21</f>
+        <v>2.3109999999999999</v>
+      </c>
+      <c r="N8" s="9">
+        <f>N21</f>
+        <v>5.6539999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="39">
-        <v>24</v>
-      </c>
-      <c r="I7" s="6" t="s">
+      <c r="G9" s="38"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="10">
+        <v>0</v>
+      </c>
+      <c r="J9" s="11">
+        <v>5.1460000000000004E-3</v>
+      </c>
+      <c r="K9" s="11">
+        <v>5.1460000000000004E-3</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0.1235</v>
+      </c>
+      <c r="N9" s="12">
+        <f>H6*K9</f>
+        <v>0.123504</v>
+      </c>
+    </row>
+    <row r="10" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="32"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="27">
+        <f>SUM(I8:I9)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="22">
+        <f>SUM(J8:J9)</f>
+        <v>5.1460000000000004E-3</v>
+      </c>
+      <c r="K10" s="22">
+        <f>SUM(K8:K9)</f>
+        <v>5.1460000000000004E-3</v>
+      </c>
+      <c r="L10" s="22">
+        <f>L8+L9</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="22">
+        <f>M8+M9</f>
+        <v>2.4344999999999999</v>
+      </c>
+      <c r="N10" s="23">
+        <f>N8+N9</f>
+        <v>5.7775039999999995</v>
+      </c>
+      <c r="O10" s="30"/>
+      <c r="P10" s="25"/>
+    </row>
+    <row r="12" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F13" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="42">
+        <v>5</v>
+      </c>
+      <c r="I13" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="8"/>
-    </row>
-    <row r="8" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F8" s="38"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="10" t="s">
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="45"/>
+      <c r="N13" s="46"/>
+    </row>
+    <row r="14" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="51"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F15" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F9" s="13" t="s">
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J15" s="18">
+        <v>0.4</v>
+      </c>
+      <c r="K15" s="18">
+        <v>0.9</v>
+      </c>
+      <c r="L15" s="18">
+        <f t="shared" ref="L15:N19" si="0">$H$13*I15</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M15" s="18">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N15" s="19">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="16" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F16" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="17">
-        <v>0</v>
-      </c>
-      <c r="M9" s="17">
-        <f>M22</f>
-        <v>2.3109999999999999</v>
-      </c>
-      <c r="N9" s="18">
-        <f>N22</f>
-        <v>5.6539999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F10" s="47" t="s">
+      <c r="G16" s="48"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="20">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F17" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="48"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="22">
-        <v>0</v>
-      </c>
-      <c r="J10" s="23">
-        <v>5.1460000000000004E-3</v>
-      </c>
-      <c r="K10" s="23">
-        <v>5.1460000000000004E-3</v>
-      </c>
-      <c r="L10" s="23">
-        <v>0</v>
-      </c>
-      <c r="M10" s="23">
-        <v>0.1235</v>
-      </c>
-      <c r="N10" s="24">
-        <f>H7*K10</f>
-        <v>0.123504</v>
-      </c>
-    </row>
-    <row r="11" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F11" s="19" t="s">
+      <c r="G17" s="48"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="20">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K17" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F18" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="50">
-        <f>SUM(I9:I10)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="34">
-        <f>SUM(J9:J10)</f>
-        <v>5.1460000000000004E-3</v>
-      </c>
-      <c r="K11" s="34">
-        <f>SUM(K9:K10)</f>
-        <v>5.1460000000000004E-3</v>
-      </c>
-      <c r="L11" s="34">
-        <f>L9+L10</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="34">
-        <f>M9+M10</f>
-        <v>2.4344999999999999</v>
-      </c>
-      <c r="N11" s="35">
-        <f>N9+N10</f>
-        <v>5.7775039999999995</v>
-      </c>
-      <c r="O11" s="53" t="str">
-        <f>" &lt;15[W]"</f>
-        <v xml:space="preserve"> &lt;15[W]</v>
-      </c>
-      <c r="P11" s="43" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F14" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="39">
-        <v>5</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="8"/>
-    </row>
-    <row r="15" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F15" s="40"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="M15" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F16" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="29">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="J16" s="30">
-        <v>0.4</v>
-      </c>
-      <c r="K16" s="30">
-        <v>0.9</v>
-      </c>
-      <c r="L16" s="30">
-        <f>$H$14*I16</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M16" s="30">
-        <f>$H$14*J16</f>
-        <v>2</v>
-      </c>
-      <c r="N16" s="31">
-        <f>$H$14*K16</f>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="17" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="32">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
-        <v>2E-3</v>
-      </c>
-      <c r="K17" s="2">
-        <v>2E-3</v>
-      </c>
-      <c r="L17" s="2">
-        <f>$H$14*I17</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="2">
-        <f>$H$14*J17</f>
-        <v>0.01</v>
-      </c>
-      <c r="N17" s="5">
-        <f>$H$14*K17</f>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="18" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F18" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="32">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="K18" s="2">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="L18" s="2">
-        <f>$H$14*I18</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="2">
-        <f>$H$14*J18</f>
-        <v>0.02</v>
-      </c>
-      <c r="N18" s="5">
-        <f>$H$14*K18</f>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="19" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="32">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="G18" s="48"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="20">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
         <f>2*0.0281</f>
         <v>5.62E-2</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K18" s="1">
         <f>8*0.0281</f>
         <v>0.2248</v>
       </c>
-      <c r="L19" s="2">
-        <f>$H$14*I19</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="2">
-        <f>$H$14*J19</f>
+      <c r="L18" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <f t="shared" si="0"/>
         <v>0.28100000000000003</v>
       </c>
-      <c r="N19" s="5">
-        <f>$H$14*K19</f>
+      <c r="N18" s="3">
+        <f t="shared" si="0"/>
         <v>1.1240000000000001</v>
       </c>
     </row>
-    <row r="20" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F20" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="32">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
+    <row r="19" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F19" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="48"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="20">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
         <f>0.0000065</f>
         <v>6.4999999999999996E-6</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K19" s="1">
         <f>0.0000065</f>
         <v>6.4999999999999996E-6</v>
       </c>
-      <c r="L20" s="2">
-        <f>$H$14*I20</f>
-        <v>0</v>
-      </c>
-      <c r="M20" s="2">
-        <f>$H$14*J20</f>
+      <c r="L19" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <f t="shared" si="0"/>
         <v>3.2499999999999997E-5</v>
       </c>
-      <c r="N20" s="5">
-        <f>$H$14*K20</f>
+      <c r="N19" s="3">
+        <f t="shared" si="0"/>
         <v>3.2499999999999997E-5</v>
       </c>
     </row>
+    <row r="20" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="11">
+        <v>0</v>
+      </c>
+      <c r="M20" s="11">
+        <f>M32</f>
+        <v>0.13439909999999999</v>
+      </c>
+      <c r="N20" s="12">
+        <f>N32</f>
+        <v>0.1356366</v>
+      </c>
+    </row>
     <row r="21" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="48"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="23">
-        <v>0</v>
-      </c>
-      <c r="M21" s="23">
-        <f>M31</f>
-        <v>2.3990999999999999E-3</v>
-      </c>
-      <c r="N21" s="24">
-        <f>N31</f>
-        <v>3.6365999999999998E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F22" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="50">
-        <f>SUM(I16:I19)</f>
+      <c r="G21" s="32"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="27">
+        <f t="shared" ref="I21:N21" si="1">SUM(I15:I18)</f>
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J22" s="34">
-        <f>SUM(J16:J19)</f>
+      <c r="J21" s="22">
+        <f t="shared" si="1"/>
         <v>0.46220000000000006</v>
       </c>
-      <c r="K22" s="34">
-        <f>SUM(K16:K19)</f>
+      <c r="K21" s="22">
+        <f t="shared" si="1"/>
         <v>1.1308</v>
       </c>
-      <c r="L22" s="34">
-        <f>SUM(L16:L19)</f>
+      <c r="L21" s="22">
+        <f t="shared" si="1"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="M22" s="34">
-        <f>SUM(M16:M19)</f>
+      <c r="M21" s="22">
+        <f t="shared" si="1"/>
         <v>2.3109999999999999</v>
       </c>
-      <c r="N22" s="35">
-        <f>SUM(N16:N19)</f>
+      <c r="N21" s="23">
+        <f t="shared" si="1"/>
         <v>5.6539999999999999</v>
       </c>
-      <c r="O22" s="53" t="str">
-        <f>" &lt;12[W]"</f>
-        <v xml:space="preserve"> &lt;12[W]</v>
-      </c>
-      <c r="P22" s="43" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F25" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="39">
+      <c r="O21" s="30"/>
+      <c r="P21" s="25"/>
+    </row>
+    <row r="23" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F24" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="42">
         <v>3.3</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I24" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M25" s="7"/>
-      <c r="N25" s="8"/>
-    </row>
-    <row r="26" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" s="23" t="s">
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="45"/>
+      <c r="N24" s="46"/>
+    </row>
+    <row r="25" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="L26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="M26" s="23" t="s">
+      <c r="J25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="N26" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="33">
-        <v>0</v>
-      </c>
-      <c r="J27" s="42">
+      <c r="M25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F26" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="21">
+        <v>0</v>
+      </c>
+      <c r="J26" s="24">
         <f>0.000635</f>
         <v>6.3500000000000004E-4</v>
       </c>
-      <c r="K27" s="42">
+      <c r="K26" s="24">
         <f>0.00074</f>
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="L27" s="30">
-        <f>$H$14*I27</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="30">
-        <f>$H$25*J27</f>
+      <c r="L26" s="18">
+        <f>$H$13*I26</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="18">
+        <f t="shared" ref="M26:N31" si="2">$H$24*J26</f>
         <v>2.0955000000000001E-3</v>
       </c>
-      <c r="N27" s="31">
-        <f>$H$25*K27</f>
+      <c r="N26" s="19">
+        <f t="shared" si="2"/>
         <v>2.4419999999999997E-3</v>
       </c>
     </row>
-    <row r="28" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F28" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="28">
+    <row r="27" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F27" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="48"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="16">
         <f>0.000002</f>
         <v>1.9999999999999999E-6</v>
       </c>
-      <c r="K28" s="28">
+      <c r="K27" s="16">
         <f>0.000002</f>
         <v>1.9999999999999999E-6</v>
       </c>
-      <c r="L28" s="2">
-        <f>$H$14*I28</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="2">
-        <f>$H$25*J28</f>
+      <c r="L27" s="1">
+        <f>$H$13*I27</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <f t="shared" si="2"/>
         <v>6.5999999999999995E-6</v>
       </c>
-      <c r="N28" s="5">
-        <f>$H$25*K28</f>
+      <c r="N27" s="3">
+        <f t="shared" si="2"/>
         <v>6.5999999999999995E-6</v>
       </c>
     </row>
+    <row r="28" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F28" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="7">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8">
+        <f>0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="K28" s="8">
+        <f>0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="L28" s="8">
+        <f>$H$13*I28</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="2"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="2"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
     <row r="29" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="28">
+      <c r="F29" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="10">
+        <v>0</v>
+      </c>
+      <c r="J29" s="11">
+        <f>0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="K29" s="11">
+        <f>0.02</f>
+        <v>0.02</v>
+      </c>
+      <c r="L29" s="11">
+        <f>$H$13*I29</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <f t="shared" si="2"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="N29" s="3">
+        <f t="shared" si="2"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F30" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="48"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="16">
         <f>0.00008</f>
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="K29" s="28">
-        <f>4*J29</f>
+      <c r="K30" s="16">
+        <f>4*J30</f>
         <v>3.2000000000000003E-4</v>
       </c>
-      <c r="L29" s="2">
-        <f>$H$14*I29</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="2">
-        <f>$H$25*J29</f>
+      <c r="L30" s="1">
+        <f>$H$13*I30</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="2"/>
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="N29" s="5">
-        <f>$H$25*K29</f>
+      <c r="N30" s="3">
+        <f t="shared" si="2"/>
         <v>1.0560000000000001E-3</v>
       </c>
     </row>
-    <row r="30" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F30" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="G30" s="48"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="22">
-        <v>0</v>
-      </c>
-      <c r="J30" s="51">
+    <row r="31" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="38"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="10">
+        <v>0</v>
+      </c>
+      <c r="J31" s="28">
         <f>0.00001</f>
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="K30" s="51">
+      <c r="K31" s="28">
         <f>4*0.00001</f>
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="L30" s="23">
-        <f>$H$14*I30</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="23">
-        <f>$H$25*J30</f>
+      <c r="L31" s="11">
+        <f>$H$13*I31</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="11">
+        <f t="shared" si="2"/>
         <v>3.3000000000000003E-5</v>
       </c>
-      <c r="N30" s="24">
-        <f>$H$25*K30</f>
+      <c r="N31" s="12">
+        <f t="shared" si="2"/>
         <v>1.3200000000000001E-4</v>
       </c>
     </row>
-    <row r="31" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F31" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="50">
-        <f>SUM(I27:I30)</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="52">
-        <f>SUM(J27:J30)</f>
-        <v>7.2700000000000011E-4</v>
-      </c>
-      <c r="K31" s="52">
-        <f>SUM(K27:K30)</f>
-        <v>1.1020000000000001E-3</v>
-      </c>
-      <c r="L31" s="34">
-        <f>SUM(L27:L30)</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="34">
-        <f>SUM(M27:M30)</f>
-        <v>2.3990999999999999E-3</v>
-      </c>
-      <c r="N31" s="35">
-        <f>SUM(N27:N30)</f>
-        <v>3.6365999999999998E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-    </row>
-    <row r="33" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F34" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="39">
-        <v>3.3</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7" t="s">
+    <row r="32" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F32" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="M34" s="7"/>
-      <c r="N34" s="8"/>
-    </row>
-    <row r="35" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F35" s="38"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="L35" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F36" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="16">
-        <v>0</v>
-      </c>
-      <c r="J36" s="17">
-        <f>0.02</f>
-        <v>0.02</v>
-      </c>
-      <c r="K36" s="17">
-        <f>0.02</f>
-        <v>0.02</v>
-      </c>
-      <c r="L36" s="17">
-        <f>$H$14*I36</f>
-        <v>0</v>
-      </c>
-      <c r="M36" s="17">
-        <f>$H$34*J36</f>
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="N36" s="18">
-        <f>H34*K36</f>
-        <v>6.6000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F37" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G37" s="48"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="22">
-        <v>0</v>
-      </c>
-      <c r="J37" s="23">
-        <f>0.02</f>
-        <v>0.02</v>
-      </c>
-      <c r="K37" s="23">
-        <f>0.02</f>
-        <v>0.02</v>
-      </c>
-      <c r="L37" s="23">
-        <f>$H$14*I37</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="23">
-        <f>$H$34*J37</f>
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="N37" s="18">
-        <f>$H$34*K37</f>
-        <v>6.6000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F38" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G38" s="20"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="50">
-        <f>SUM(I36:I37)</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="34">
-        <f>SUM(J36:J37)</f>
-        <v>0.04</v>
-      </c>
-      <c r="K38" s="34">
-        <f>SUM(K36:K37)</f>
-        <v>0.04</v>
-      </c>
-      <c r="L38" s="34">
-        <f>SUM(L36:L37)</f>
-        <v>0</v>
-      </c>
-      <c r="M38" s="34">
-        <f>SUM(M36:M37)</f>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="N38" s="35">
-        <f>SUM(N36:N37)</f>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="O38" s="53" t="str">
-        <f>" &lt;0.99[W]"</f>
-        <v xml:space="preserve"> &lt;0.99[W]</v>
-      </c>
-      <c r="P38" s="43" t="s">
-        <v>34</v>
-      </c>
+      <c r="G32" s="32"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="27">
+        <f t="shared" ref="I32:N32" si="3">SUM(I26:I31)</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="29">
+        <f t="shared" si="3"/>
+        <v>4.0726999999999999E-2</v>
+      </c>
+      <c r="K32" s="29">
+        <f t="shared" si="3"/>
+        <v>4.1102E-2</v>
+      </c>
+      <c r="L32" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="22">
+        <f t="shared" si="3"/>
+        <v>0.13439909999999999</v>
+      </c>
+      <c r="N32" s="23">
+        <f t="shared" si="3"/>
+        <v>0.1356366</v>
+      </c>
+      <c r="O32" s="30"/>
+      <c r="P32" s="25"/>
+    </row>
+    <row r="33" spans="6:14" x14ac:dyDescent="0.25">
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="L34:N34"/>
+  <mergeCells count="32">
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F32:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
